--- a/docs/verification/files/rocscience/joints/rj015.xlsx
+++ b/docs/verification/files/rocscience/joints/rj015.xlsx
@@ -3454,7 +3454,11 @@
       <c r="C23" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="1"/>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>

--- a/docs/verification/files/rocscience/joints/rj015.xlsx
+++ b/docs/verification/files/rocscience/joints/rj015.xlsx
@@ -3374,7 +3374,9 @@
       <c r="G16" t="s">
         <v>34</v>
       </c>
-      <c r="D16"/>
+      <c r="D16">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
